--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="495">
   <si>
     <t>Filename</t>
   </si>
@@ -811,685 +811,694 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.8140,0.0169,0.0800,0.0029</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.6226,0.0002,0.0001,0.5267</t>
-  </si>
-  <si>
-    <t>0.0074,0.0000,0.0000,0.9987</t>
+    <t>0.9855,0.0021,0.0033,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9783,0.0004,0.0004,0.0132</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0002,0.9995</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8108,0.0038,0.1434,0.0011</t>
+  </si>
+  <si>
+    <t>0.0036,0.0007,0.9949,0.0001</t>
+  </si>
+  <si>
+    <t>0.6965,0.0003,0.5316,0.0000</t>
+  </si>
+  <si>
+    <t>0.0074,0.0024,0.9877,0.0003</t>
+  </si>
+  <si>
+    <t>0.3703,0.0002,0.6069,0.0019</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0051,0.9928,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.5091,0.0003,0.4627,0.0017</t>
+  </si>
+  <si>
+    <t>0.0952,0.0007,0.8810,0.0014</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0006,0.9954,0.0005</t>
+  </si>
+  <si>
+    <t>0.0219,0.0001,0.9839,0.0002</t>
+  </si>
+  <si>
+    <t>0.0067,0.0007,0.9833,0.0057</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0681,0.9479,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.4750,0.2544,0.1310,0.0008</t>
+  </si>
+  <si>
+    <t>0.0016,0.0011,0.9983,0.0022</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9948,0.0010,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.0662,0.9406,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9985,0.0641,0.0000</t>
+  </si>
+  <si>
+    <t>0.0088,0.9431,0.0316,0.0011</t>
+  </si>
+  <si>
+    <t>0.0031,0.0023,0.9923,0.0003</t>
+  </si>
+  <si>
+    <t>0.0358,0.0792,0.8423,0.0023</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0038,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0021,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0006,0.9897,0.0279</t>
+  </si>
+  <si>
+    <t>0.0008,0.9217,0.0002,0.8289</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0052,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0108,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9996,0.0036</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0014,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9893,0.0147,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,0.9999,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9582,0.0584,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9685,0.9970,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9974,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.9992,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0001,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.0682,0.0005,0.9540,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0017,0.9994,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9883,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9889,0.9884,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.8500,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9933,0.9821,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0004,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0036,0.9992</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9403,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9927,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9585,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9957,0.9974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9908,0.9707,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0043,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9940,0.0038,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0011,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0014,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9991,0.0005,0.0000,0.0000</t>
+    <t>0.9963,0.0034,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0013,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0022,0.0004,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.9330,0.0033,0.0127,0.0057</t>
+  </si>
+  <si>
+    <t>0.8904,0.0001,0.1350,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9987,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9992,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1470,0.8686,0.0027,0.0002</t>
+  </si>
+  <si>
+    <t>0.4733,0.0115,0.3886,0.0018</t>
+  </si>
+  <si>
+    <t>0.9771,0.0002,0.0220,0.0001</t>
+  </si>
+  <si>
+    <t>0.9552,0.0065,0.0028,0.0015</t>
+  </si>
+  <si>
+    <t>0.9191,0.0004,0.0399,0.0036</t>
+  </si>
+  <si>
+    <t>0.0001,0.4103,0.0002,0.9956</t>
+  </si>
+  <si>
+    <t>0.0002,0.9990,0.0028,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9971,0.9708,0.0000</t>
+  </si>
+  <si>
+    <t>0.5337,0.5421,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.6882,0.3395,0.0027,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.5979,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9941,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0030,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0453,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4807,0.0004,0.5696,0.0006</t>
+  </si>
+  <si>
+    <t>0.2573,0.0001,0.8207,0.0001</t>
+  </si>
+  <si>
+    <t>0.9010,0.0013,0.0683,0.0036</t>
+  </si>
+  <si>
+    <t>0.0067,0.0000,0.0000,0.9988</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9807,0.9810,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0029,0.9950,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.8428,0.2845,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.5392,0.0001,0.0018,0.4684</t>
+  </si>
+  <si>
+    <t>0.0003,0.0013,0.9989,0.0016</t>
+  </si>
+  <si>
+    <t>0.9975,0.0000,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0119,0.9725,0.0127,0.0003</t>
+  </si>
+  <si>
+    <t>0.9963,0.0002,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9869,0.0029,0.0022,0.0005</t>
+  </si>
+  <si>
+    <t>0.0360,0.0321,0.8020,0.0037</t>
+  </si>
+  <si>
+    <t>0.9268,0.0104,0.0371,0.0002</t>
+  </si>
+  <si>
+    <t>0.9865,0.0025,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9943,0.0017,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9875,0.0050,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.5219,0.6254,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8251,0.2148,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0167,0.0019,0.9818,0.0010</t>
+  </si>
+  <si>
+    <t>0.9172,0.1250,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0003,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9942,0.0029,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9865,0.0013,0.0068,0.0011</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.9766,0.0213,0.0055,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0014,0.9975,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.4281,0.9853,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0398,0.0024,0.9520,0.0007</t>
+  </si>
+  <si>
+    <t>0.0064,0.0003,0.9925,0.0003</t>
+  </si>
+  <si>
+    <t>0.0029,0.0061,0.9891,0.0008</t>
+  </si>
+  <si>
+    <t>0.0377,0.0129,0.9230,0.0003</t>
+  </si>
+  <si>
+    <t>0.0330,0.1658,0.5485,0.0008</t>
+  </si>
+  <si>
+    <t>0.8644,0.0012,0.1875,0.0003</t>
+  </si>
+  <si>
+    <t>0.9012,0.0035,0.0395,0.0066</t>
+  </si>
+  <si>
+    <t>0.0298,0.0113,0.9475,0.0008</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9991,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4610,0.6460,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0837,0.9464,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0160,0.9842,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8971,0.0647,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9056,0.0004,0.1353,0.0002</t>
+  </si>
+  <si>
+    <t>0.8460,0.0034,0.0367,0.0101</t>
+  </si>
+  <si>
+    <t>0.8867,0.0109,0.0689,0.0013</t>
+  </si>
+  <si>
+    <t>0.7642,0.0002,0.2728,0.0005</t>
+  </si>
+  <si>
+    <t>0.0011,0.0003,0.9984,0.0003</t>
+  </si>
+  <si>
+    <t>0.0031,0.0020,0.9848,0.0008</t>
+  </si>
+  <si>
+    <t>0.0004,0.0046,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0010,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0022,0.9963,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0006,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9675,0.0262,0.0040,0.0024</t>
+  </si>
+  <si>
+    <t>0.9981,0.0011,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9262,0.0182,0.0048,0.0017</t>
-  </si>
-  <si>
-    <t>0.1232,0.0022,0.8965,0.0002</t>
-  </si>
-  <si>
-    <t>0.3279,0.0003,0.8230,0.0001</t>
-  </si>
-  <si>
-    <t>0.8996,0.0004,0.0848,0.0010</t>
-  </si>
-  <si>
-    <t>0.9431,0.0015,0.0317,0.0012</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0073,0.9923,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.2757,0.0002,0.7152,0.0011</t>
-  </si>
-  <si>
-    <t>0.0352,0.0006,0.9603,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.0020,0.9941,0.0002</t>
-  </si>
-  <si>
-    <t>0.8557,0.0000,0.2684,0.0001</t>
-  </si>
-  <si>
-    <t>0.0019,0.0000,0.9973,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0838,0.9201,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9138,0.0063,0.0455,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9996,0.0009</t>
-  </si>
-  <si>
-    <t>0.0008,0.9980,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.9921,0.0032,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9451,0.0017,0.0327,0.0011</t>
-  </si>
-  <si>
-    <t>0.0127,0.9872,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9983,0.0755,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.9905,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.0017,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0095,0.0040,0.9765,0.0008</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9954,0.0008</t>
-  </si>
-  <si>
-    <t>0.0007,0.0015,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9988,0.0027</t>
-  </si>
-  <si>
-    <t>0.0009,0.9144,0.0013,0.9587</t>
-  </si>
-  <si>
-    <t>0.0010,0.9909,0.0000,0.0022</t>
-  </si>
-  <si>
-    <t>0.0003,0.9985,0.0058,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0031,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0025,0.9996,0.0003</t>
-  </si>
-  <si>
-    <t>0.2835,0.0000,0.8141,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0006,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0012,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9769,0.0273,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.3881,0.9939,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0081,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9987,0.0019</t>
-  </si>
-  <si>
-    <t>0.0000,0.9972,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.9991,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9680,0.0001,0.0465,0.0001</t>
-  </si>
-  <si>
-    <t>0.0077,0.0008,0.9920,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0145,0.9996,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9328,0.8470,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.8585,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.9963,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.0003,0.9994</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0047,0.9989</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0006,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9885,0.9776,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9920,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.4980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9760,0.6084,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9967,0.0032,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0023,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9848,0.0185,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9963,0.0020,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.0110,0.0003,0.9919,0.0006</t>
-  </si>
-  <si>
-    <t>0.0044,0.0010,0.9934,0.0003</t>
-  </si>
-  <si>
-    <t>0.9474,0.0013,0.0215,0.0024</t>
-  </si>
-  <si>
-    <t>0.1858,0.0001,0.7821,0.0013</t>
-  </si>
-  <si>
-    <t>0.0007,0.9983,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0235,0.9750,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.3724,0.0011,0.5621,0.0027</t>
-  </si>
-  <si>
-    <t>0.1423,0.0001,0.8772,0.0004</t>
-  </si>
-  <si>
-    <t>0.5445,0.0078,0.3036,0.0035</t>
-  </si>
-  <si>
-    <t>0.1272,0.0072,0.8221,0.0047</t>
-  </si>
-  <si>
-    <t>0.0002,0.9747,0.0015,0.7486</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.9893,0.0000</t>
-  </si>
-  <si>
-    <t>0.9777,0.0228,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.3785,0.6121,0.0080,0.0004</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9955,0.0009,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9306,0.9958,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9519,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6442,0.0003,0.3966,0.0005</t>
-  </si>
-  <si>
-    <t>0.0571,0.0003,0.9593,0.0001</t>
-  </si>
-  <si>
-    <t>0.6375,0.0013,0.3092,0.0036</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.0003,0.9958,0.0547,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0083,0.9882,0.0007,0.0018</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0255,0.9790,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9937,0.0000,0.0033,0.0006</t>
-  </si>
-  <si>
-    <t>0.1755,0.0001,0.0012,0.8928</t>
-  </si>
-  <si>
-    <t>0.0009,0.0021,0.9980,0.0010</t>
-  </si>
-  <si>
-    <t>0.9983,0.0000,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0000,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.1009,0.2292,0.3081,0.0006</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9821,0.0060,0.0044,0.0002</t>
-  </si>
-  <si>
-    <t>0.0085,0.9715,0.0132,0.0060</t>
-  </si>
-  <si>
-    <t>0.7730,0.0395,0.1080,0.0002</t>
-  </si>
-  <si>
-    <t>0.9951,0.0005,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0006,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9621,0.0253,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.7814,0.3028,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9804,0.0160,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0115,0.0015,0.9883,0.0004</t>
-  </si>
-  <si>
-    <t>0.9731,0.0364,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0005,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9946,0.0038,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9833,0.0019,0.0091,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9943,0.0011,0.0025,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0218,0.9957,0.0016</t>
-  </si>
-  <si>
-    <t>0.0021,0.0022,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.6851,0.9680,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0480,0.0068,0.9272,0.0013</t>
-  </si>
-  <si>
-    <t>0.0163,0.0008,0.9816,0.0003</t>
-  </si>
-  <si>
-    <t>0.0063,0.0078,0.9849,0.0005</t>
-  </si>
-  <si>
-    <t>0.0903,0.0019,0.9290,0.0002</t>
-  </si>
-  <si>
-    <t>0.0183,0.0830,0.7973,0.0030</t>
-  </si>
-  <si>
-    <t>0.9592,0.0020,0.0306,0.0002</t>
-  </si>
-  <si>
-    <t>0.9589,0.0056,0.0062,0.0022</t>
-  </si>
-  <si>
-    <t>0.0833,0.0073,0.8971,0.0012</t>
-  </si>
-  <si>
-    <t>0.0013,0.9978,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8899,0.1945,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0640,0.9610,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.9979,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9628,0.0048,0.0054,0.0007</t>
-  </si>
-  <si>
-    <t>0.9950,0.0001,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9693,0.0026,0.0043,0.0018</t>
-  </si>
-  <si>
-    <t>0.9436,0.0041,0.0236,0.0016</t>
-  </si>
-  <si>
-    <t>0.8921,0.0015,0.1038,0.0007</t>
-  </si>
-  <si>
-    <t>0.0011,0.0004,0.9982,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0011,0.9982,0.0005</t>
-  </si>
-  <si>
-    <t>0.0046,0.0419,0.9794,0.0006</t>
-  </si>
-  <si>
-    <t>0.0011,0.0003,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0128,0.9956,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9964,0.0021,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9876,0.0104,0.0006,0.0005</t>
+    <t>0.9981,0.0012,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9992,0.0005,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9989,0.0004</t>
-  </si>
-  <si>
-    <t>0.0136,0.0082,0.9660,0.0012</t>
-  </si>
-  <si>
-    <t>0.9552,0.0007,0.0126,0.0064</t>
-  </si>
-  <si>
-    <t>0.0024,0.0002,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0025,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.6302,0.9087,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0217,0.0012,0.9757,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0007,0.9960,0.0015</t>
-  </si>
-  <si>
-    <t>0.0019,0.0017,0.9927,0.0008</t>
-  </si>
-  <si>
-    <t>0.8707,0.0005,0.1178,0.0008</t>
-  </si>
-  <si>
-    <t>0.9905,0.0001,0.0065,0.0001</t>
-  </si>
-  <si>
-    <t>0.9869,0.0009,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9960,0.0044,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9895,0.0117,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0027,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0012,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.1412,0.9450,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0063,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0577,0.9973,0.0007</t>
-  </si>
-  <si>
-    <t>0.0067,0.0139,0.9738,0.0008</t>
-  </si>
-  <si>
-    <t>0.0105,0.0014,0.2964,0.3923</t>
-  </si>
-  <si>
-    <t>0.0026,0.0003,0.9951,0.0004</t>
-  </si>
-  <si>
-    <t>0.0076,0.0014,0.9815,0.0027</t>
-  </si>
-  <si>
-    <t>0.8904,0.0000,0.0104,0.0343</t>
-  </si>
-  <si>
-    <t>0.0004,0.0013,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9870,0.0001,0.0001,0.0058</t>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0047,0.9971,0.0006</t>
+  </si>
+  <si>
+    <t>0.0493,0.5134,0.3315,0.0007</t>
+  </si>
+  <si>
+    <t>0.9757,0.0005,0.0119,0.0009</t>
+  </si>
+  <si>
+    <t>0.0213,0.0019,0.9839,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.1676,0.9823,0.0006</t>
+  </si>
+  <si>
+    <t>0.0097,0.0001,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0110,0.0003,0.9868,0.0009</t>
+  </si>
+  <si>
+    <t>0.0007,0.0035,0.9971,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.0278,0.9948,0.0003</t>
+  </si>
+  <si>
+    <t>0.6609,0.0003,0.3356,0.0008</t>
+  </si>
+  <si>
+    <t>0.9734,0.0001,0.0192,0.0005</t>
+  </si>
+  <si>
+    <t>0.9975,0.0001,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9938,0.0059,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0025,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.0018,0.9927,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0032,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0589,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.0031,0.9909,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9992,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9964,0.0078</t>
+  </si>
+  <si>
+    <t>0.9362,0.0005,0.0434,0.0014</t>
+  </si>
+  <si>
+    <t>0.0014,0.0012,0.9932,0.0020</t>
+  </si>
+  <si>
+    <t>0.9941,0.0000,0.0003,0.0041</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0022,0.0001,0.0000,0.9993</t>
+  </si>
+  <si>
+    <t>0.9961,0.0002,0.0001,0.0005</t>
   </si>
 </sst>
 </file>
@@ -1900,7 +1909,7 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
         <v>267</v>
@@ -1945,7 +1954,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2082,10 +2091,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2096,10 +2105,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2180,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2236,10 +2245,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2267,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2365,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2379,7 +2388,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2449,7 +2458,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2477,7 +2486,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2575,7 +2584,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2726,10 +2735,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>266</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3034,10 +3043,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>272</v>
+        <v>348</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3163,7 +3172,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>275</v>
+        <v>353</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>272</v>
+        <v>354</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3356,10 +3365,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>311</v>
+        <v>279</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>285</v>
+        <v>361</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3468,10 +3477,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3482,10 +3491,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3510,10 +3519,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3524,10 +3533,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3541,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3583,7 +3592,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3597,7 +3606,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>311</v>
+        <v>282</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3608,10 +3617,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3622,10 +3631,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>271</v>
+        <v>321</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3818,10 +3827,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>341</v>
+        <v>393</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3916,10 +3925,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3972,10 +3981,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4000,10 +4009,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4070,10 +4079,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4087,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4112,10 +4121,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>269</v>
+        <v>411</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4199,7 +4208,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>319</v>
+        <v>417</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4280,10 +4289,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4353,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4395,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4448,10 +4457,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>429</v>
+        <v>309</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4591,7 +4600,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4633,7 +4642,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>331</v>
+        <v>443</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4661,7 +4670,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4717,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4815,7 +4824,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>453</v>
+        <v>417</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4952,10 +4961,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5008,10 +5017,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5039,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>469</v>
+        <v>309</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>350</v>
+        <v>269</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5193,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>380</v>
+        <v>269</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>429</v>
+        <v>487</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5316,10 +5325,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5330,10 +5339,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D249" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5403,7 +5412,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -811,694 +811,694 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9855,0.0021,0.0033,0.0008</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.8964,0.0087,0.0097,0.0164</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9109,0.0002,0.0003,0.1047</t>
+  </si>
+  <si>
+    <t>0.0107,0.0000,0.0003,0.9964</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0006,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9819,0.0018,0.0064,0.0002</t>
+  </si>
+  <si>
+    <t>0.0644,0.0012,0.9430,0.0004</t>
+  </si>
+  <si>
+    <t>0.0091,0.0011,0.9926,0.0000</t>
+  </si>
+  <si>
+    <t>0.0454,0.0013,0.9531,0.0008</t>
+  </si>
+  <si>
+    <t>0.9709,0.0021,0.0161,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0054,0.9930,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9624,0.0006,0.0146,0.0020</t>
+  </si>
+  <si>
+    <t>0.0053,0.0001,0.9931,0.0002</t>
+  </si>
+  <si>
+    <t>0.0021,0.0001,0.9971,0.0004</t>
+  </si>
+  <si>
+    <t>0.0028,0.0002,0.9955,0.0003</t>
+  </si>
+  <si>
+    <t>0.1809,0.0001,0.9001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0075,0.0003,0.9842,0.0017</t>
+  </si>
+  <si>
+    <t>0.0068,0.0000,0.9942,0.0005</t>
+  </si>
+  <si>
+    <t>0.1244,0.9014,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.7144,0.0744,0.1354,0.0026</t>
+  </si>
+  <si>
+    <t>0.0006,0.0013,0.9993,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9926,0.0023,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9928,0.0008,0.0041,0.0002</t>
+  </si>
+  <si>
+    <t>0.0152,0.9828,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9966,0.3021,0.0000</t>
+  </si>
+  <si>
+    <t>0.0057,0.9560,0.0276,0.0010</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9982,0.0003</t>
+  </si>
+  <si>
+    <t>0.0091,0.0024,0.9828,0.0003</t>
+  </si>
+  <si>
+    <t>0.0092,0.0000,0.9445,0.0022</t>
+  </si>
+  <si>
+    <t>0.0011,0.0097,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9993,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9709,0.0004,0.9779</t>
+  </si>
+  <si>
+    <t>0.0004,0.9962,0.0000,0.0017</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0021,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0189,0.9997,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9495,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0011,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0226,0.9980,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9986,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9841,0.0006,0.0102,0.0002</t>
+  </si>
+  <si>
+    <t>0.2895,0.0005,0.7963,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0029,0.9992,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9911,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.8967,0.9505,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.2613,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9972,0.0497,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0003,0.0020,0.9983</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0058,0.9996</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.0002,0.9996</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.0000,0.9999</t>
   </si>
   <si>
-    <t>0.9783,0.0004,0.0004,0.0132</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.0002,0.9995</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8108,0.0038,0.1434,0.0011</t>
-  </si>
-  <si>
-    <t>0.0036,0.0007,0.9949,0.0001</t>
-  </si>
-  <si>
-    <t>0.6965,0.0003,0.5316,0.0000</t>
-  </si>
-  <si>
-    <t>0.0074,0.0024,0.9877,0.0003</t>
-  </si>
-  <si>
-    <t>0.3703,0.0002,0.6069,0.0019</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0051,0.9928,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.5091,0.0003,0.4627,0.0017</t>
-  </si>
-  <si>
-    <t>0.0952,0.0007,0.8810,0.0014</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0006,0.9954,0.0005</t>
-  </si>
-  <si>
-    <t>0.0219,0.0001,0.9839,0.0002</t>
-  </si>
-  <si>
-    <t>0.0067,0.0007,0.9833,0.0057</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0681,0.9479,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.4750,0.2544,0.1310,0.0008</t>
-  </si>
-  <si>
-    <t>0.0016,0.0011,0.9983,0.0022</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9948,0.0010,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.0662,0.9406,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9985,0.0641,0.0000</t>
-  </si>
-  <si>
-    <t>0.0088,0.9431,0.0316,0.0011</t>
-  </si>
-  <si>
-    <t>0.0031,0.0023,0.9923,0.0003</t>
-  </si>
-  <si>
-    <t>0.0358,0.0792,0.8423,0.0023</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0038,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0006,0.9897,0.0279</t>
-  </si>
-  <si>
-    <t>0.0008,0.9217,0.0002,0.8289</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0052,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0108,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9996,0.0036</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0007,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9893,0.0147,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9582,0.0584,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9685,0.9970,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0014,0.0000</t>
+    <t>0.0000,0.9978,0.9959,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9256,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9948,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9978,0.9963,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9937,0.2960,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9872,0.0179,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0014,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9920,0.0056,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0012,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9926,0.0084,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.0002,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.9813,0.0004,0.0061,0.0007</t>
+  </si>
+  <si>
+    <t>0.1672,0.0001,0.8698,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9979,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9972,0.0001,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0682,0.0005,0.9540,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0017,0.9994,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.9883,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9889,0.9884,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.8500,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9933,0.9821,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0004,0.9996</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0036,0.9992</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0002,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9403,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9927,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.9585,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9957,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9908,0.9707,0.0000</t>
-  </si>
-  <si>
-    <t>0.9962,0.0043,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9940,0.0038,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0011,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0014,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9963,0.0034,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0013,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.0004,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.9330,0.0033,0.0127,0.0057</t>
-  </si>
-  <si>
-    <t>0.8904,0.0001,0.1350,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9987,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.1470,0.8686,0.0027,0.0002</t>
-  </si>
-  <si>
-    <t>0.4733,0.0115,0.3886,0.0018</t>
-  </si>
-  <si>
-    <t>0.9771,0.0002,0.0220,0.0001</t>
-  </si>
-  <si>
-    <t>0.9552,0.0065,0.0028,0.0015</t>
-  </si>
-  <si>
-    <t>0.9191,0.0004,0.0399,0.0036</t>
-  </si>
-  <si>
-    <t>0.0001,0.4103,0.0002,0.9956</t>
-  </si>
-  <si>
-    <t>0.0002,0.9990,0.0028,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9971,0.9708,0.0000</t>
-  </si>
-  <si>
-    <t>0.5337,0.5421,0.0037,0.0001</t>
-  </si>
-  <si>
-    <t>0.6882,0.3395,0.0027,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.5979,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9941,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0030,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0453,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4807,0.0004,0.5696,0.0006</t>
-  </si>
-  <si>
-    <t>0.2573,0.0001,0.8207,0.0001</t>
-  </si>
-  <si>
-    <t>0.9010,0.0013,0.0683,0.0036</t>
-  </si>
-  <si>
-    <t>0.0067,0.0000,0.0000,0.9988</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9807,0.9810,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0029,0.9950,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.8428,0.2845,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.5392,0.0001,0.0018,0.4684</t>
-  </si>
-  <si>
-    <t>0.0003,0.0013,0.9989,0.0016</t>
-  </si>
-  <si>
-    <t>0.9975,0.0000,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0119,0.9725,0.0127,0.0003</t>
-  </si>
-  <si>
-    <t>0.9963,0.0002,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9869,0.0029,0.0022,0.0005</t>
-  </si>
-  <si>
-    <t>0.0360,0.0321,0.8020,0.0037</t>
-  </si>
-  <si>
-    <t>0.9268,0.0104,0.0371,0.0002</t>
-  </si>
-  <si>
-    <t>0.9865,0.0025,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9943,0.0017,0.0009,0.0012</t>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1793,0.8453,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.9641,0.0005,0.0224,0.0010</t>
+  </si>
+  <si>
+    <t>0.7819,0.0005,0.2181,0.0004</t>
+  </si>
+  <si>
+    <t>0.9090,0.0023,0.0292,0.0065</t>
+  </si>
+  <si>
+    <t>0.9233,0.0068,0.0246,0.0040</t>
+  </si>
+  <si>
+    <t>0.0005,0.3034,0.0009,0.9903</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9975,0.9917,0.0000</t>
+  </si>
+  <si>
+    <t>0.7685,0.2638,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.4779,0.6357,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9958,0.0003,0.0005,0.0020</t>
   </si>
   <si>
     <t>0.9997,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9993,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0005,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.6395,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9945,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0021,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0026,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.9961,0.0006,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0222,0.0011,0.9639,0.0013</t>
+  </si>
+  <si>
+    <t>0.3968,0.0001,0.7713,0.0000</t>
+  </si>
+  <si>
+    <t>0.9826,0.0005,0.0046,0.0008</t>
+  </si>
+  <si>
+    <t>0.0033,0.0000,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.9979,0.1420,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.9938,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.1932,0.8661,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9780,0.0007,0.0103,0.0013</t>
+  </si>
+  <si>
+    <t>0.9016,0.0001,0.0004,0.0912</t>
+  </si>
+  <si>
+    <t>0.0004,0.0016,0.9988,0.0009</t>
+  </si>
+  <si>
+    <t>0.9920,0.0000,0.0027,0.0013</t>
+  </si>
+  <si>
+    <t>0.9818,0.0000,0.0151,0.0004</t>
+  </si>
+  <si>
+    <t>0.0549,0.8749,0.0277,0.0003</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9679,0.0097,0.0067,0.0008</t>
+  </si>
+  <si>
+    <t>0.1378,0.7630,0.0108,0.0073</t>
+  </si>
+  <si>
+    <t>0.8382,0.0466,0.0508,0.0007</t>
+  </si>
+  <si>
+    <t>0.9923,0.0015,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0004,0.0004,0.0003</t>
+  </si>
+  <si>
     <t>0.9998,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9875,0.0050,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.5219,0.6254,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8251,0.2148,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0167,0.0019,0.9818,0.0010</t>
-  </si>
-  <si>
-    <t>0.9172,0.1250,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9964,0.0003,0.0005,0.0016</t>
-  </si>
-  <si>
-    <t>0.9942,0.0029,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9865,0.0013,0.0068,0.0011</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.9766,0.0213,0.0055,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0014,0.9975,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.4281,0.9853,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0398,0.0024,0.9520,0.0007</t>
-  </si>
-  <si>
-    <t>0.0064,0.0003,0.9925,0.0003</t>
-  </si>
-  <si>
-    <t>0.0029,0.0061,0.9891,0.0008</t>
-  </si>
-  <si>
-    <t>0.0377,0.0129,0.9230,0.0003</t>
-  </si>
-  <si>
-    <t>0.0330,0.1658,0.5485,0.0008</t>
-  </si>
-  <si>
-    <t>0.8644,0.0012,0.1875,0.0003</t>
-  </si>
-  <si>
-    <t>0.9012,0.0035,0.0395,0.0066</t>
-  </si>
-  <si>
-    <t>0.0298,0.0113,0.9475,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9991,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4610,0.6460,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0837,0.9464,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0160,0.9842,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8971,0.0647,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9056,0.0004,0.1353,0.0002</t>
-  </si>
-  <si>
-    <t>0.8460,0.0034,0.0367,0.0101</t>
-  </si>
-  <si>
-    <t>0.8867,0.0109,0.0689,0.0013</t>
-  </si>
-  <si>
-    <t>0.7642,0.0002,0.2728,0.0005</t>
-  </si>
-  <si>
-    <t>0.0011,0.0003,0.9984,0.0003</t>
-  </si>
-  <si>
-    <t>0.0031,0.0020,0.9848,0.0008</t>
-  </si>
-  <si>
-    <t>0.0004,0.0046,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0010,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0022,0.9963,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0006,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9675,0.0262,0.0040,0.0024</t>
-  </si>
-  <si>
-    <t>0.9981,0.0011,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0047,0.9971,0.0006</t>
-  </si>
-  <si>
-    <t>0.0493,0.5134,0.3315,0.0007</t>
-  </si>
-  <si>
-    <t>0.9757,0.0005,0.0119,0.0009</t>
-  </si>
-  <si>
-    <t>0.0213,0.0019,0.9839,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0007,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.1676,0.9823,0.0006</t>
-  </si>
-  <si>
-    <t>0.0097,0.0001,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0110,0.0003,0.9868,0.0009</t>
-  </si>
-  <si>
-    <t>0.0007,0.0035,0.9971,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.0278,0.9948,0.0003</t>
-  </si>
-  <si>
-    <t>0.6609,0.0003,0.3356,0.0008</t>
-  </si>
-  <si>
-    <t>0.9734,0.0001,0.0192,0.0005</t>
-  </si>
-  <si>
-    <t>0.9975,0.0001,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9938,0.0059,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0025,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.0018,0.9927,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0032,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0589,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0028,0.0031,0.9909,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9992,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9964,0.0078</t>
-  </si>
-  <si>
-    <t>0.9362,0.0005,0.0434,0.0014</t>
-  </si>
-  <si>
-    <t>0.0014,0.0012,0.9932,0.0020</t>
-  </si>
-  <si>
-    <t>0.9941,0.0000,0.0003,0.0041</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0022,0.0001,0.0000,0.9993</t>
-  </si>
-  <si>
-    <t>0.9961,0.0002,0.0001,0.0005</t>
+    <t>0.9966,0.0013,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0042,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.8934,0.1766,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.6901,0.4040,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9642,0.0003,0.0204,0.0012</t>
+  </si>
+  <si>
+    <t>0.9630,0.0519,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0009,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9417,0.0301,0.0167,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9896,0.0077,0.0027,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.9979,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.6091,0.9948,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0086,0.0034,0.9772,0.0013</t>
+  </si>
+  <si>
+    <t>0.4111,0.0072,0.5227,0.0026</t>
+  </si>
+  <si>
+    <t>0.0005,0.0011,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0177,0.0018,0.9758,0.0004</t>
+  </si>
+  <si>
+    <t>0.0310,0.0114,0.9351,0.0003</t>
+  </si>
+  <si>
+    <t>0.5446,0.0014,0.5795,0.0003</t>
+  </si>
+  <si>
+    <t>0.8178,0.0049,0.0581,0.0078</t>
+  </si>
+  <si>
+    <t>0.5490,0.0045,0.4217,0.0020</t>
+  </si>
+  <si>
+    <t>0.0062,0.9927,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9987,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7915,0.2776,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.3771,0.7367,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.9965,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9892,0.0006,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.3580,0.0005,0.6342,0.0010</t>
+  </si>
+  <si>
+    <t>0.9709,0.0020,0.0058,0.0012</t>
+  </si>
+  <si>
+    <t>0.7613,0.0061,0.1894,0.0055</t>
+  </si>
+  <si>
+    <t>0.3290,0.0035,0.6680,0.0010</t>
+  </si>
+  <si>
+    <t>0.0033,0.0006,0.9963,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9994,0.0006</t>
+  </si>
+  <si>
+    <t>0.0026,0.0106,0.9864,0.0017</t>
+  </si>
+  <si>
+    <t>0.0017,0.0007,0.9966,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0040,0.9974,0.0004</t>
+  </si>
+  <si>
+    <t>0.9975,0.0008,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9764,0.0189,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9953,0.0029,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0083,0.0276,0.9661,0.0009</t>
+  </si>
+  <si>
+    <t>0.9838,0.0005,0.0066,0.0011</t>
+  </si>
+  <si>
+    <t>0.0046,0.0001,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0015,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.6490,0.7337,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0069,0.0009,0.9880,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9977,0.0018</t>
+  </si>
+  <si>
+    <t>0.0004,0.0092,0.9974,0.0002</t>
+  </si>
+  <si>
+    <t>0.3604,0.0024,0.5121,0.0033</t>
+  </si>
+  <si>
+    <t>0.9764,0.0010,0.0072,0.0012</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0029,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0009,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0013,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9942,0.0041,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0079,0.9932,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0018,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9009,0.9952,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0095,0.9942,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0242,0.0003,0.8853,0.0128</t>
+  </si>
+  <si>
+    <t>0.2819,0.0017,0.6830,0.0017</t>
+  </si>
+  <si>
+    <t>0.0046,0.0006,0.9860,0.0052</t>
+  </si>
+  <si>
+    <t>0.9977,0.0001,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0072,0.0000,0.0000,0.9987</t>
+  </si>
+  <si>
+    <t>0.9968,0.0002,0.0000,0.0003</t>
   </si>
 </sst>
 </file>
@@ -1884,7 +1884,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1898,7 +1898,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1912,7 +1912,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1926,7 +1926,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1940,7 +1940,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1954,7 +1954,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1968,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1982,7 +1982,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1996,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2010,7 +2010,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2024,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2038,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2052,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2066,7 +2066,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2080,7 +2080,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2094,7 +2094,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2105,10 +2105,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2122,7 +2122,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2136,7 +2136,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2150,7 +2150,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2164,7 +2164,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2178,7 +2178,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2192,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2206,7 +2206,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2220,7 +2220,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2234,7 +2234,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2248,7 +2248,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2262,7 +2262,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2276,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2290,7 +2290,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2304,7 +2304,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2318,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2332,7 +2332,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2346,7 +2346,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2360,7 +2360,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2374,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2388,7 +2388,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2402,7 +2402,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2416,7 +2416,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2430,7 +2430,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2444,7 +2444,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2458,7 +2458,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2472,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2486,7 +2486,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2500,7 +2500,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2514,7 +2514,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2528,7 +2528,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2542,7 +2542,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2556,7 +2556,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2570,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2584,7 +2584,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2598,7 +2598,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2612,7 +2612,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2626,7 +2626,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2640,7 +2640,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2654,7 +2654,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2668,7 +2668,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2682,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2696,7 +2696,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2710,7 +2710,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2724,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2738,7 +2738,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2752,7 +2752,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2766,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2780,7 +2780,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2794,7 +2794,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2808,7 +2808,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2822,7 +2822,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2836,7 +2836,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2850,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2864,7 +2864,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2878,7 +2878,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2892,7 +2892,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2903,10 +2903,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2917,10 +2917,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2934,7 +2934,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2948,7 +2948,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2962,7 +2962,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2976,7 +2976,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2990,7 +2990,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3004,7 +3004,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>266</v>
+        <v>344</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3018,7 +3018,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3032,7 +3032,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3046,7 +3046,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3060,7 +3060,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3074,7 +3074,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3085,10 +3085,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3116,7 +3116,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>269</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3130,7 +3130,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3144,7 +3144,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3158,7 +3158,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3172,7 +3172,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3186,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3200,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3214,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3228,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>353</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3242,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3270,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>354</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3284,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3298,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3312,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3326,7 +3326,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3340,7 +3340,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3354,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3365,10 +3365,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3382,7 +3382,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>279</v>
+        <v>364</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3396,7 +3396,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>361</v>
+        <v>281</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3410,7 +3410,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3424,7 +3424,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3438,7 +3438,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3452,7 +3452,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3466,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3480,7 +3480,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3494,7 +3494,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3508,7 +3508,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3522,7 +3522,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3536,7 +3536,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3550,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3564,7 +3564,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3578,7 +3578,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3592,7 +3592,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3606,7 +3606,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>282</v>
+        <v>364</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3617,10 +3617,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3631,10 +3631,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3648,7 +3648,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3662,7 +3662,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3676,7 +3676,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3690,7 +3690,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3704,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3718,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3732,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3746,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3760,7 +3760,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3774,7 +3774,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3788,7 +3788,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3802,7 +3802,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3816,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3830,7 +3830,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3844,7 +3844,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3858,7 +3858,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3872,7 +3872,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3886,7 +3886,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>392</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3900,7 +3900,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>392</v>
+        <v>340</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3914,7 +3914,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>393</v>
+        <v>341</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3925,10 +3925,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3942,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>395</v>
+        <v>324</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3956,7 +3956,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3970,7 +3970,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3981,10 +3981,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3998,7 +3998,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4012,7 +4012,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4026,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4040,7 +4040,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4054,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4068,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4082,7 +4082,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4096,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4110,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4121,10 +4121,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4138,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4152,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4166,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>410</v>
+        <v>270</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4222,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>414</v>
+        <v>270</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4236,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4250,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>416</v>
+        <v>324</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4264,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4278,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4289,10 +4289,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4306,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4317,10 +4317,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4334,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4348,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4362,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4376,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4390,7 +4390,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4404,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4418,7 +4418,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4432,7 +4432,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4446,7 +4446,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4457,10 +4457,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4474,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4488,7 +4488,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>309</v>
+        <v>431</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4502,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4516,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4530,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4544,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4558,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4572,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4583,10 +4583,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D195" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4600,7 +4600,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4611,10 +4611,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4628,7 +4628,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4642,7 +4642,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4653,10 +4653,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4670,7 +4670,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4684,7 +4684,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4698,7 +4698,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4709,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4726,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4740,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4751,10 +4751,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4768,7 +4768,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4782,7 +4782,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4796,7 +4796,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4810,7 +4810,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4824,7 +4824,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4838,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>417</v>
+        <v>271</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4852,7 +4852,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4866,7 +4866,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4880,7 +4880,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4894,7 +4894,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4908,7 +4908,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4922,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4936,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4950,7 +4950,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4961,10 +4961,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4978,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4992,7 +4992,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5006,7 +5006,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5017,10 +5017,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5034,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5048,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5062,7 +5062,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>309</v>
+        <v>471</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5101,7 +5101,7 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
         <v>474</v>
@@ -5174,7 +5174,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5202,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5283,7 +5283,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D245" t="s">
         <v>485</v>
@@ -5339,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>489</v>
@@ -5412,7 +5412,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>392</v>
+        <v>341</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5426,7 +5426,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>392</v>
+        <v>341</v>
       </c>
     </row>
     <row r="256" spans="1:4">
